--- a/data/trans_orig/P70B_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P70B_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según como se adapta su horario laboral a sus compromisos sociales y familiares fuera del trabajo en 2023</t>
+          <t>Población según como se adapta su horario laboral a sus compromisos sociales y familiares fuera del trabajo en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9649</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>6019</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>155</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9438</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10309</t>
+          <t>10297</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39070</t>
+          <t>37943</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17264</t>
+          <t>17365</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>17630</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51234</t>
+          <t>51814</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36326</t>
+          <t>37133</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66266</t>
+          <t>67172</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27703</t>
+          <t>27708</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50452</t>
+          <t>51127</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>71997</t>
+          <t>72915</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>108922</t>
+          <t>111135</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>65,75%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24489</t>
+          <t>22385</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21107</t>
+          <t>21748</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43681</t>
+          <t>43887</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29802</t>
+          <t>28516</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62089</t>
+          <t>59770</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5842</t>
+          <t>7563</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>775</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9788</t>
+          <t>9364</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29929</t>
+          <t>31020</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63805</t>
+          <t>65566</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20215</t>
+          <t>19493</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57349</t>
+          <t>58393</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59764</t>
+          <t>60884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110772</t>
+          <t>110388</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>176016</t>
+          <t>174765</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>224224</t>
+          <t>224537</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91308</t>
+          <t>84205</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>221701</t>
+          <t>220538</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>266215</t>
+          <t>259647</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>424192</t>
+          <t>422783</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,12%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80585</t>
+          <t>81246</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>124354</t>
+          <t>126738</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>77337</t>
+          <t>78202</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>239570</t>
+          <t>248531</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>177657</t>
+          <t>181410</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>367184</t>
+          <t>377979</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>53,75%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10658</t>
+          <t>11165</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29125</t>
+          <t>29542</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14801</t>
+          <t>14778</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18230</t>
+          <t>17726</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38026</t>
+          <t>38961</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47382</t>
+          <t>45883</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>78874</t>
+          <t>77669</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39990</t>
+          <t>40853</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61577</t>
+          <t>62180</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>94630</t>
+          <t>92652</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>131996</t>
+          <t>130667</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>235761</t>
+          <t>238044</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>280639</t>
+          <t>282794</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,82 +2109,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>61,45%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>209487</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>194277</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>224620</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>59,84%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>55,49%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>64,16%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>468135</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>438983</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>494193</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>57,77%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>54,18%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>60,99%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>209487</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>194031</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>224773</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>59,84%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>55,42%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>64,2%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>468135</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>441421</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>494640</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>57,77%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>54,48%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>61,05%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103284</t>
+          <t>102102</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>145271</t>
+          <t>141305</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68258</t>
+          <t>68627</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>94237</t>
+          <t>95018</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>181196</t>
+          <t>181118</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>229178</t>
+          <t>229607</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,34%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5991</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33808</t>
+          <t>32771</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36923</t>
+          <t>38595</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16638</t>
+          <t>17053</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54919</t>
+          <t>55094</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20595</t>
+          <t>20016</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83155</t>
+          <t>82171</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35183</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58694</t>
+          <t>58671</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53511</t>
+          <t>47813</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>133010</t>
+          <t>128092</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>447726</t>
+          <t>449887</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>663214</t>
+          <t>665330</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>261000</t>
+          <t>262641</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>324823</t>
+          <t>322351</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>728360</t>
+          <t>732230</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1004357</t>
+          <t>1009263</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>50583</t>
+          <t>54353</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>195888</t>
+          <t>195715</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>82505</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>121506</t>
+          <t>120859</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>123553</t>
+          <t>122916</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>299446</t>
+          <t>297449</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13032</t>
+          <t>13179</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11558</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>8295</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21232</t>
+          <t>21775</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23661</t>
+          <t>23829</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43724</t>
+          <t>43562</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14136</t>
+          <t>14426</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27763</t>
+          <t>27351</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40793</t>
+          <t>41476</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>65962</t>
+          <t>65305</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>177814</t>
+          <t>178400</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>209143</t>
+          <t>209699</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>117116</t>
+          <t>116551</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>137218</t>
+          <t>136281</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>303840</t>
+          <t>301035</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>340558</t>
+          <t>340262</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,05%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>54409</t>
+          <t>52257</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>81450</t>
+          <t>80919</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>45301</t>
+          <t>45379</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>64303</t>
+          <t>63541</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>103373</t>
+          <t>104378</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>136618</t>
+          <t>139283</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,45%</t>
         </is>
       </c>
     </row>
@@ -3575,97 +3575,97 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1153</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>892</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>1022</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>10287</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10269</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>18891</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>54,45%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>12926</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7011</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12641</t>
+          <t>12774</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>14537</t>
+          <t>15108</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>23458</t>
+          <t>23863</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>68,78%</t>
         </is>
       </c>
     </row>
@@ -4144,97 +4144,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="W34" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -4257,97 +4257,97 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
+      <c r="W35" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -4370,97 +4370,97 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
           <t>1598</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="W36" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>1598</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>1598</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
     </row>
@@ -4483,97 +4483,97 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>29662</t>
+          <t>27930</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>64621</t>
+          <t>62642</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>26720</t>
+          <t>26185</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>58279</t>
+          <t>61858</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>62709</t>
+          <t>61724</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>106336</t>
+          <t>106059</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>142719</t>
+          <t>138148</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>259661</t>
+          <t>261414</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>141400</t>
+          <t>139382</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>195911</t>
+          <t>195893</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>298039</t>
+          <t>301128</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>433254</t>
+          <t>433433</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1151413</t>
+          <t>1149872</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1485142</t>
+          <t>1541874</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>718174</t>
+          <t>692169</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>899564</t>
+          <t>901657</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1966278</t>
+          <t>1955952</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2344802</t>
+          <t>2380011</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>69,48%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>300865</t>
+          <t>276008</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>515387</t>
+          <t>512482</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>355791</t>
+          <t>357222</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>568702</t>
+          <t>594142</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>698987</t>
+          <t>686233</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>997183</t>
+          <t>1003424</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70B_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P70B_2023-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9265</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22639</t>
+          <t>20686</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10297</t>
+          <t>9244</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37943</t>
+          <t>36568</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8573</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17365</t>
+          <t>19519</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>31212</t>
+          <t>30728</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17630</t>
+          <t>18079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51814</t>
+          <t>50136</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>52567</t>
+          <t>54905</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37133</t>
+          <t>39985</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67172</t>
+          <t>69187</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>38902</t>
+          <t>45349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27708</t>
+          <t>32588</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51127</t>
+          <t>58010</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91470</t>
+          <t>100254</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>72915</t>
+          <t>81665</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>111135</t>
+          <t>121378</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>62,62%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10819</t>
+          <t>21470</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22385</t>
+          <t>41421</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32553</t>
+          <t>35167</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21748</t>
+          <t>23240</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43887</t>
+          <t>48137</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>43372</t>
+          <t>56637</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28516</t>
+          <t>38498</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59770</t>
+          <t>77083</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>39,77%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>87787</t>
+          <t>102075</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87787</t>
+          <t>102075</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87787</t>
+          <t>102075</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>169026</t>
+          <t>193818</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>169026</t>
+          <t>193818</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>169026</t>
+          <t>193818</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7563</t>
+          <t>10854</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>991</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9364</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>6643</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11781</t>
+          <t>15261</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>45719</t>
+          <t>51520</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31020</t>
+          <t>35644</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65566</t>
+          <t>73128</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40522</t>
+          <t>42218</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19493</t>
+          <t>29148</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58393</t>
+          <t>54828</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>86241</t>
+          <t>93739</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60884</t>
+          <t>73669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110388</t>
+          <t>117770</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>200092</t>
+          <t>228002</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>174765</t>
+          <t>203271</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>224537</t>
+          <t>252546</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>172005</t>
+          <t>197719</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84205</t>
+          <t>179480</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>220538</t>
+          <t>214334</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>372096</t>
+          <t>425722</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>259647</t>
+          <t>393010</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>422783</t>
+          <t>460418</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>64,38%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>103183</t>
+          <t>113461</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81246</t>
+          <t>89834</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>126738</t>
+          <t>137697</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,67 +1668,67 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>136704</t>
+          <t>75561</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78202</t>
+          <t>60667</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>248531</t>
+          <t>94314</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
+          <t>19,01%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>29,55%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>189021</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>158481</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>216486</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>26,43%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>22,16%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>70,42%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>239887</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>181410</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>377979</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>34,11%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>25,8%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>30,27%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>395920</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>395920</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>395920</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>352916</t>
+          <t>319205</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>352916</t>
+          <t>319205</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>352916</t>
+          <t>319205</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>703258</t>
+          <t>715125</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>703258</t>
+          <t>715125</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>703258</t>
+          <t>715125</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18002</t>
+          <t>18801</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11165</t>
+          <t>10669</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29542</t>
+          <t>32118</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8636</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>16407</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>26639</t>
+          <t>28455</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17726</t>
+          <t>19146</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38961</t>
+          <t>41066</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60967</t>
+          <t>64950</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45883</t>
+          <t>48773</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>77669</t>
+          <t>82568</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,22 +2011,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50465</t>
+          <t>56904</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>40853</t>
+          <t>46174</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62180</t>
+          <t>70179</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>111431</t>
+          <t>121853</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>92652</t>
+          <t>104064</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>130667</t>
+          <t>146101</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>258648</t>
+          <t>298470</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>238044</t>
+          <t>272371</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>282794</t>
+          <t>320376</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>209487</t>
+          <t>238680</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>194277</t>
+          <t>222249</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>224620</t>
+          <t>255679</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>468135</t>
+          <t>537150</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>438983</t>
+          <t>506604</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>494193</t>
+          <t>564314</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,67%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>122558</t>
+          <t>152307</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>102102</t>
+          <t>132169</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>141305</t>
+          <t>175557</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>81516</t>
+          <t>90372</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68627</t>
+          <t>77473</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>95018</t>
+          <t>106184</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>204074</t>
+          <t>242679</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>181118</t>
+          <t>215175</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>229607</t>
+          <t>271811</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>460175</t>
+          <t>534528</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>460175</t>
+          <t>534528</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>460175</t>
+          <t>534528</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>350104</t>
+          <t>395610</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>350104</t>
+          <t>395610</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>350104</t>
+          <t>395610</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>810279</t>
+          <t>930137</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>810279</t>
+          <t>930137</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>810279</t>
+          <t>930137</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17912</t>
+          <t>19588</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>10745</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32771</t>
+          <t>29853</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16468</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8640</t>
+          <t>8167</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38595</t>
+          <t>20002</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>34379</t>
+          <t>32716</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17053</t>
+          <t>23217</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55094</t>
+          <t>45328</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>50597</t>
+          <t>54208</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>41127</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82171</t>
+          <t>68729</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>47730</t>
+          <t>51603</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>41891</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58671</t>
+          <t>63343</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>98328</t>
+          <t>105811</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47813</t>
+          <t>88865</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>128092</t>
+          <t>124709</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>553074</t>
+          <t>335383</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>449887</t>
+          <t>309342</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>665330</t>
+          <t>357862</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>284125</t>
+          <t>275463</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>262641</t>
+          <t>258475</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>322351</t>
+          <t>291082</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>837198</t>
+          <t>610846</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>732230</t>
+          <t>582335</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1009263</t>
+          <t>639835</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>64,02%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>124684</t>
+          <t>135480</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54353</t>
+          <t>115355</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>195715</t>
+          <t>157690</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>104453</t>
+          <t>114636</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>82505</t>
+          <t>100762</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>120859</t>
+          <t>131144</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>229137</t>
+          <t>250116</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>122916</t>
+          <t>225720</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>297449</t>
+          <t>277844</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>746266</t>
+          <t>544659</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>746266</t>
+          <t>544659</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>746266</t>
+          <t>544659</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>452776</t>
+          <t>454829</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>452776</t>
+          <t>454829</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>452776</t>
+          <t>454829</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1199042</t>
+          <t>999488</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1199042</t>
+          <t>999488</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1199042</t>
+          <t>999488</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>7127</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13179</t>
+          <t>13182</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>7433</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11067</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>13743</t>
+          <t>14559</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>9379</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21775</t>
+          <t>22888</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>32786</t>
+          <t>34662</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23829</t>
+          <t>24509</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43562</t>
+          <t>46102</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>21703</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14426</t>
+          <t>15305</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27351</t>
+          <t>29772</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>52713</t>
+          <t>56365</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41476</t>
+          <t>44673</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>65305</t>
+          <t>70042</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>194131</t>
+          <t>216529</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>178400</t>
+          <t>201122</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>209699</t>
+          <t>233479</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>126891</t>
+          <t>140329</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>116551</t>
+          <t>128773</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>136281</t>
+          <t>151312</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>321022</t>
+          <t>356857</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>301035</t>
+          <t>337112</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>340262</t>
+          <t>378721</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,44%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>66155</t>
+          <t>71086</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>52257</t>
+          <t>57474</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>80919</t>
+          <t>88063</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>53846</t>
+          <t>62712</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>45379</t>
+          <t>52942</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>63541</t>
+          <t>73580</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>120002</t>
+          <t>133798</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>104378</t>
+          <t>116753</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>139283</t>
+          <t>152005</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>300304</t>
+          <t>329404</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>300304</t>
+          <t>329404</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>300304</t>
+          <t>329404</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>207175</t>
+          <t>232176</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>207175</t>
+          <t>232176</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>207175</t>
+          <t>232176</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>507479</t>
+          <t>561580</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>507479</t>
+          <t>561580</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>507479</t>
+          <t>561580</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>719</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>569</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3728,12 +3728,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10619</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>7311</t>
+          <t>8119</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10287</t>
+          <t>11321</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>15705</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>18891</t>
+          <t>21212</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,55%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>9646</t>
+          <t>10861</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12926</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>11032</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>7782</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>14109</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>19520</t>
+          <t>21894</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>15108</t>
+          <t>16748</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>23863</t>
+          <t>26544</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>46258</t>
+          <t>53465</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>27930</t>
+          <t>38678</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>62642</t>
+          <t>71824</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>36509</t>
+          <t>35108</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>26185</t>
+          <t>25585</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>61858</t>
+          <t>45610</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>82767</t>
+          <t>88572</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>61724</t>
+          <t>70269</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>106059</t>
+          <t>110924</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -4821,102 +4821,102 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>212874</t>
+          <t>226746</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>138148</t>
+          <t>193173</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>261414</t>
+          <t>260955</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
+          <t>11,76%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>13,54%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>183037</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>161238</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>207654</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>12,1%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>13,72%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>409783</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>373013</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>450079</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11,91%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
           <t>10,84%</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>13,31%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>167782</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>139382</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>195893</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>11,48%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>9,53%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>13,4%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>380657</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>301128</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>433433</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>1267240</t>
+          <t>1142692</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1149872</t>
+          <t>1090903</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1541874</t>
+          <t>1185697</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>838722</t>
+          <t>905658</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>692169</t>
+          <t>869067</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>901657</t>
+          <t>938821</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>2105962</t>
+          <t>2048350</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1955952</t>
+          <t>1986938</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2380011</t>
+          <t>2109219</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>61,3%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>437044</t>
+          <t>504666</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>276008</t>
+          <t>466686</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>512482</t>
+          <t>552089</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>418948</t>
+          <t>389479</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>357222</t>
+          <t>357676</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>594142</t>
+          <t>417242</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>855992</t>
+          <t>894145</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>686233</t>
+          <t>842349</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1003424</t>
+          <t>952063</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1963416</t>
+          <t>1927568</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1963416</t>
+          <t>1927568</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1963416</t>
+          <t>1927568</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1461961</t>
+          <t>1513282</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1461961</t>
+          <t>1513282</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1461961</t>
+          <t>1513282</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>3425377</t>
+          <t>3440851</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3425377</t>
+          <t>3440851</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3425377</t>
+          <t>3440851</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
